--- a/Results/friedman_test_results.xlsx
+++ b/Results/friedman_test_results.xlsx
@@ -14,15 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Metric</t>
   </si>
   <si>
-    <t>Number_of_models</t>
-  </si>
-  <si>
-    <t>Number_of_outer_folds</t>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>Outer_folds</t>
   </si>
   <si>
     <t>Friedman_statistic</t>
@@ -31,10 +31,13 @@
     <t>p_value</t>
   </si>
   <si>
-    <t>Significant_at_0.05</t>
+    <t>Inference</t>
   </si>
   <si>
     <t>ROC_AUC</t>
+  </si>
+  <si>
+    <t>exploratory; overlapping training sets do not provide independent replicates</t>
   </si>
 </sst>
 </file>
@@ -426,13 +429,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>24.78016726403823</v>
+        <v>15.68100358422939</v>
       </c>
       <c r="E2">
-        <v>0.0008299707766726284</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
+        <v>0.02819602170464636</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
